--- a/calibration/phase2_bayesian_regression/owner_group/FI/FI_prob_metrics.xlsx
+++ b/calibration/phase2_bayesian_regression/owner_group/FI/FI_prob_metrics.xlsx
@@ -115,61 +115,52 @@
     <t>beta</t>
   </si>
   <si>
-    <t>{'a': 2.842542480051846, 'b': -0.936234685653131, 'c': 0.573431063809015}</t>
-  </si>
-  <si>
-    <t>{'a': -1.016540741538179, 'b': -4.045087503301989, 'c': -4.041195455027108}</t>
-  </si>
-  <si>
-    <t>[0.23780891 0.14968069 0.42702505 0.27982958 0.13320466 0.14198147
- 0.13320466 0.31311606 0.10600455 0.0992479  0.44069927 0.16353645
- 0.15749488 0.43634066 0.67146539 0.3889457  0.33314525 0.15064485
- 0.19024395 0.39091101 0.52369523 0.39302231 0.10852778 0.6030048
- 0.26087426 0.152913   0.12557816 0.18717874 0.2119408  0.35524801
- 0.25490429 0.53024505 0.12403352 0.17408034 0.29031866 0.31577289
- 0.2043818  0.26258005 0.12435612 0.13203166 0.24549353 0.1373947
- 0.03914581 0.31231847 0.11355585 0.02410757 0.42070891 0.37831259
- 0.63625228 0.33725673 0.34839544 0.20551641 0.11340364 0.72578037
- 0.4049348  0.14138699 0.1478149  0.10188215 0.32525711 0.11011985
- 0.38043127 0.35407434 0.06466306 0.12758498 0.09335763 0.35616368
- 0.45513922 0.10171184 0.40577803 0.31830361 0.24763443 0.13613023
- 0.15930622 0.18776605 0.647404   0.47131976 0.15234324 0.16318301
- 0.22092713 0.18703132 0.42117032 0.24418309 0.39518162 0.41363394
- 0.21450632 0.35988817 0.21266877 0.39363427 0.53597227 0.34752969
- 0.08793346 0.11844155 0.31721803 0.16738075 0.13613023 0.13492944
- 0.22017312 0.11228577 0.11969274 0.28177973 0.07566228 0.48742302
- 0.38611231 0.54204479 0.23241707 0.48019353 0.41213322 0.27653875
- 0.20216335 0.10006764 0.16353645 0.20293126 0.16353645 0.41393351
- 0.22138541 0.49002713 0.19100857 0.45198498 0.22985429 0.73822248
- 0.3045917  0.37681259 0.38557713 0.49570853 0.26357281 0.529745
- 0.33109118 0.23998535 0.27713362 0.26357281 0.06564194 0.28973139
- 0.65539976 0.09323504 0.18449929 0.45560497 0.26258005 0.65149934]</t>
-  </si>
-  <si>
-    <t>[0.20616409 0.35313842 0.38821706 0.42557037 0.26598483 0.28777584
- 0.31400278 0.33811736 0.5631033  0.6489011  0.613929   0.3518417
- 0.2030585  0.6402365  0.33745807 0.41324162 0.27541482 0.4812211
- 0.2695696  0.2628894  0.48594669 0.20180047 0.22370261 0.37004608
- 0.30665264 0.42561644 0.45037287 0.31242737 0.7007505  0.27759668
- 0.19065619 0.22346634 0.23212804 0.35920835 0.5600475  0.94847983
- 0.30822018 0.38472712 0.26042512 0.18291214 0.3231302  0.5958266
- 0.32106945 0.37004608 0.5391371  0.46665204 0.65873444 0.25582042
- 0.60455555 0.22081812 0.6954226  0.34010515 0.59366304 0.31520838
- 0.45843485 0.27823937 0.7775484  0.46766645 0.60910726 0.6552482
- 0.23804913 0.3388158  0.273094   0.3214704  0.2402124  0.7215029
- 0.3399348  0.432019   0.5548837  0.7148498  0.57191765 0.5246358
- 0.65878236 0.25073788 0.40739742 0.3842941  0.21664457 0.39483628
- 0.6272818  0.44568253 0.3159855  0.28715834 0.68144506 0.48995844
- 0.5676913  0.32897782 0.3528329  0.34390953 0.7339584  0.36667985
- 0.22238034 0.5983726  0.21147306 0.2504455  0.19411866 0.6118389
- 0.5958266  0.25596428 0.19333443 0.34219342 0.32600272 0.36593005
- 0.2223803  0.28348392 0.2795619  0.37709743 0.25645965 0.9332327
- 0.35964638 0.27141234 0.3062957  0.6451262  0.38610336 0.57386035
- 0.24714467 0.66605246 0.41324162 0.23196404 0.45501307 0.37528613
- 0.44406006 0.18893705 0.21074511 0.5587405  0.3352191  0.34600058
- 0.40197664 0.26609117 0.28010562 0.29265636 0.62231094 0.5344525
- 0.19333443 0.32393247 0.1821437  0.27375785 0.46339163 0.45928025
- 0.19086705 0.25942206]</t>
+    <t>{'a': -11.550615821163833, 'b': -15.107366102364264, 'c': -19.710303652730733}</t>
+  </si>
+  <si>
+    <t>{'a': -5.287221164095079, 'b': -7.730577295584453, 'c': -9.74025764453314}</t>
+  </si>
+  <si>
+    <t>[0.1922945  0.21519018 0.63827893 0.20605362 0.23711639 0.76983845
+ 0.24205971 0.20470091 0.18870101 0.29086355 0.22947446 0.18744341
+ 0.34677812 0.20556387 0.20748726 0.25890245 0.2041838  0.28433558
+ 0.30966976 0.36719165 0.32344582 0.34876933 0.19018082 0.92258109
+ 0.41013284 0.20421238 0.29398991 0.49676018 0.21675416 0.58299802
+ 0.39101928 0.1904504  0.18876544 0.20276168 0.18688458 0.20198725
+ 0.19423574 0.75792344 0.18873503 0.18928207 0.19497277 0.97673052
+ 0.18850734 0.4118702  0.22961954 0.18876544 0.18868024 0.24774525
+ 0.57685695 0.56348563 0.42314443 0.20603614 0.26999243 0.20549607
+ 0.34127714 0.19727096 0.21286994 0.76753499 0.18811059 0.2631231
+ 0.24210917 0.34832216 0.18735502 0.20384576 0.21184153 0.23151549
+ 0.38657371 0.20320183 0.21348701 0.43423233 0.21855437 0.1960781
+ 0.18695052 0.18764172 0.18868024 0.30382538 0.20732748 0.18693053
+ 0.38671724 0.18702044 0.82165764 0.19128457 0.23711639 0.21011342
+ 0.34003504 0.18809387 0.18702804 0.27588622 0.1869855  0.18955138
+ 0.19573551 0.18955138 0.41288574 0.24056905 0.26345018 0.51276998
+ 0.19730226 0.97599358 0.20553795 0.18741133 0.37778693 0.20686163
+ 0.99916426 0.2134777  0.19012267 0.22537402 0.58989198 0.19156269
+ 0.19079038 0.18789685 0.19596662]</t>
+  </si>
+  <si>
+    <t>[0.35250273 0.43778616 0.28482458 0.2795883  0.29531166 0.2940178
+ 0.30752206 0.5935175  0.34039396 0.3214469  0.3376385  0.28321418
+ 0.39101344 0.2949887  0.2894831  0.37649843 0.34246308 0.28014264
+ 0.36311322 0.5501037  0.29034144 0.33539167 0.33323616 0.38501668
+ 0.3437233  0.34715596 0.29568133 0.28626198 0.2793784  0.44693995
+ 0.41183794 0.3029863  0.47947058 0.38307208 0.61950636 0.2850498
+ 0.5724754  0.35889575 0.5078145  0.2857099  0.27985442 0.28673258
+ 0.281976   0.32637647 0.28011262 0.2865282  0.2996939  0.28718296
+ 0.51360583 0.2869154  0.311826   0.51929444 0.28848964 0.8186868
+ 0.46689212 0.3005234  0.3005234  0.45638588 0.31490234 0.3194182
+ 0.9152562  0.9850214  0.6226767  0.29817995 0.29786593 0.28073806
+ 0.2985437  0.2858473  0.3865162  0.28362343 0.32398993 0.4012167
+ 0.43778616 0.5659724  0.29739103 0.2851429  0.33088553 0.62488747
+ 0.30782682 0.32570985 0.32852018 0.4055713  0.31641877 0.28089368
+ 0.2794174  0.4255656  0.28878254 0.32333836 0.40247494 0.4766922
+ 0.36454093 0.750884   0.36398283 0.28061983 0.27935997 0.2802138
+ 0.5342682  0.30227378 0.2985437  0.46777284 0.4463986  0.8086401
+ 0.7728871  0.31549335 0.7359116  0.30457348 0.8103482  0.38227344
+ 0.42235154 0.58148277 0.2793928  0.28584322]</t>
   </si>
 </sst>
 </file>
@@ -609,49 +600,49 @@
     </row>
     <row r="2" spans="1:25">
       <c r="A2">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="B2">
-        <v>0.2826086956521739</v>
+        <v>0.3063063063063063</v>
       </c>
       <c r="C2">
-        <v>0.2138400226831436</v>
+        <v>0.229565441608429</v>
       </c>
       <c r="D2">
-        <v>0.2027410207939508</v>
+        <v>0.2124827530232936</v>
       </c>
       <c r="E2">
-        <v>-0.0547447272669741</v>
+        <v>-0.08039564784471098</v>
       </c>
       <c r="F2">
-        <v>0.6181308599621438</v>
+        <v>0.6508305115715484</v>
       </c>
       <c r="G2">
-        <v>0.1937973546809044</v>
+        <v>0.2095053942353876</v>
       </c>
       <c r="H2">
-        <v>0.2696865200996399</v>
+        <v>0.2506728172302246</v>
       </c>
       <c r="I2">
-        <v>0.03902108270827356</v>
+        <v>0.04887492557010781</v>
       </c>
       <c r="J2">
-        <v>0.02649071490419639</v>
+        <v>0.03065969620023674</v>
       </c>
       <c r="K2">
-        <v>0.2027410207939508</v>
+        <v>0.2124827530232936</v>
       </c>
       <c r="L2">
-        <v>0.7145817145817146</v>
+        <v>0.6879297173414821</v>
       </c>
       <c r="M2">
-        <v>0.5145283365072439</v>
+        <v>0.6110921008022491</v>
       </c>
       <c r="N2">
-        <v>0.2373597025871277</v>
+        <v>0.2429322302341461</v>
       </c>
       <c r="O2">
-        <v>0.1067372262477875</v>
+        <v>0.0840340182185173</v>
       </c>
       <c r="P2">
         <v>10</v>
@@ -674,49 +665,49 @@
     </row>
     <row r="3" spans="1:25">
       <c r="A3">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="B3">
-        <v>0.2826086956521739</v>
+        <v>0.3063063063063063</v>
       </c>
       <c r="C3">
-        <v>0.1784257255057584</v>
+        <v>0.1762965450773679</v>
       </c>
       <c r="D3">
-        <v>0.2027410207939508</v>
+        <v>0.2124827530232936</v>
       </c>
       <c r="E3">
-        <v>0.1199327851510843</v>
+        <v>0.1703018594735484</v>
       </c>
       <c r="F3">
-        <v>0.5324035706807424</v>
+        <v>0.5324485900131312</v>
       </c>
       <c r="G3">
-        <v>0.05053284269818881</v>
+        <v>0.09118987828439752</v>
       </c>
       <c r="H3">
-        <v>0.2679985742902251</v>
+        <v>0.3617210681728442</v>
       </c>
       <c r="I3">
-        <v>0.004697040362616948</v>
+        <v>0.009537474935582007</v>
       </c>
       <c r="J3">
-        <v>0.02531123538850211</v>
+        <v>0.04266277331537714</v>
       </c>
       <c r="K3">
-        <v>0.2027410207939508</v>
+        <v>0.2124827530232936</v>
       </c>
       <c r="L3">
-        <v>0.7145817145817146</v>
+        <v>0.6787624140565317</v>
       </c>
       <c r="M3">
-        <v>0.5145283365072439</v>
+        <v>0.6065872034781129</v>
       </c>
       <c r="N3">
-        <v>0.177456756417758</v>
+        <v>0.1762560430145861</v>
       </c>
       <c r="O3">
-        <v>0.1590102825933285</v>
+        <v>0.1903345445848304</v>
       </c>
       <c r="P3">
         <v>10</v>
@@ -745,49 +736,49 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="B4">
-        <v>0.3285714285714286</v>
+        <v>0.2767857142857143</v>
       </c>
       <c r="C4">
-        <v>0.2314896732568741</v>
+        <v>0.2404579967260361</v>
       </c>
       <c r="D4">
-        <v>0.2206122448979592</v>
+        <v>0.2001753826530612</v>
       </c>
       <c r="E4">
-        <v>-0.0493056419599287</v>
+        <v>-0.2012366033179596</v>
       </c>
       <c r="F4">
-        <v>0.6558314734612937</v>
+        <v>0.6747461826264426</v>
       </c>
       <c r="G4">
-        <v>0.175346183351108</v>
+        <v>0.2491937771971736</v>
       </c>
       <c r="H4">
-        <v>0.2509080767631531</v>
+        <v>0.8092299103736877</v>
       </c>
       <c r="I4">
-        <v>0.03733388232622432</v>
+        <v>0.06883008222882445</v>
       </c>
       <c r="J4">
-        <v>0.02887738477600229</v>
+        <v>0.02614838549055986</v>
       </c>
       <c r="K4">
-        <v>0.2206122448979592</v>
+        <v>0.2001753826530612</v>
       </c>
       <c r="L4">
-        <v>0.6689407955596669</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="M4">
-        <v>0.530018590458126</v>
+        <v>0.4685118303164616</v>
       </c>
       <c r="N4">
-        <v>0.2357246726751328</v>
+        <v>0.2402908951044083</v>
       </c>
       <c r="O4">
-        <v>0.119200088083744</v>
+        <v>0.09847182780504227</v>
       </c>
       <c r="P4">
         <v>10</v>
@@ -810,49 +801,49 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="B5">
-        <v>0.3285714285714286</v>
+        <v>0.2767857142857143</v>
       </c>
       <c r="C5">
-        <v>0.2054634690284729</v>
+        <v>0.1954196244478226</v>
       </c>
       <c r="D5">
-        <v>0.2206122448979592</v>
+        <v>0.2001753826530612</v>
       </c>
       <c r="E5">
-        <v>0.06866697665169552</v>
+        <v>0.02375795735822928</v>
       </c>
       <c r="F5">
-        <v>0.6050146442763572</v>
+        <v>0.5958214317762774</v>
       </c>
       <c r="G5">
-        <v>0.09761378318071368</v>
+        <v>0.1266948761684554</v>
       </c>
       <c r="H5">
-        <v>0.4408562779426575</v>
+        <v>0.6223568320274353</v>
       </c>
       <c r="I5">
-        <v>0.01248085187839074</v>
+        <v>0.0265093644906983</v>
       </c>
       <c r="J5">
-        <v>0.02781028808284447</v>
+        <v>0.03135365914383772</v>
       </c>
       <c r="K5">
-        <v>0.2206122448979592</v>
+        <v>0.2001753826530612</v>
       </c>
       <c r="L5">
-        <v>0.6689407955596669</v>
+        <v>0.6622859418558343</v>
       </c>
       <c r="M5">
-        <v>0.530018590458126</v>
+        <v>0.4749938078362895</v>
       </c>
       <c r="N5">
-        <v>0.2123580425977707</v>
+        <v>0.2155411541461945</v>
       </c>
       <c r="O5">
-        <v>0.1662404835224152</v>
+        <v>0.151223286986351</v>
       </c>
       <c r="P5">
         <v>10</v>
